--- a/data/trans_camb/IP2005-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP2005-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>3.107535742963885</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.05553122345723915</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>4.403544955207106</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.8749516312987038</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>3.719345669643248</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.4413671385574913</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-1.535659616167611</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-9.01993564220543</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.09045082258263609</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-9.808721237852289</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.3703930074764439</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-6.260915882632374</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>8.280334964362581</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.635993561599928</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.26341456198481</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6.365933625371291</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>7.208466982805311</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>4.590046195933458</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.03619676835627136</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.0006468311222399312</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.05127692154756799</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.01018834294015064</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.04331663590015854</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.005140296529906425</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.01734241064938795</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.1014929198319291</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.0004800985856662674</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.1136837732622905</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.004168624557549568</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.07200715224180151</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.09984281869459478</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.07889384117326438</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.1236065156779604</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.07493600321145111</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.08555101209485051</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.05373903739154683</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-0.5168217138860953</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.230961201816251</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4.085887147724687</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.8794653180227097</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1.772612670448936</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-1.495923128259791</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-4.852226012055487</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-7.58748634849003</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.5134867290722515</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-6.475083694210691</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-1.221231809005083</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-5.194574791278117</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>3.810932022601078</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.909316248815815</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>8.57251504455774</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.208864590517776</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>4.984995441370206</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1.933725780812095</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.005533373301235859</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.02388587944070751</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.04558045056481556</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.009810947782521819</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.01936654901987491</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.01634359782956455</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.05147446907233606</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.08015695460515981</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.004089004667569798</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.06991671819024403</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.01301933913023784</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.05612970499703554</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.04203804182036579</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.02096440119465171</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.1007172416672488</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.04845302211679881</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.05569707356209561</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.02145819736456021</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>0.2614844808349615</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2.391647709398337</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.05948995040063743</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-5.913679679291695</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.1798645207788274</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-4.097156549462577</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-5.466896068457423</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-7.124154353000423</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.896651593021843</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-10.91661740200006</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-3.118305251421224</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-7.482756748797188</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>5.336462531184679</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.851447611638274</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.535819973802325</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-1.624307649192112</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>3.411499794000843</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>-0.7371881318520928</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>0.002817640939292457</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.02577133632117558</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.0006192349111468742</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.06155589113952312</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.001905484978042888</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.04340528206388759</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.05791145143102988</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.07413065360286339</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.03976661728125003</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.1120558794700535</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.0327063246570729</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.07789405218748337</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.06002835128889213</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.03162017578934211</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.03771680263373407</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>-0.01714838579931487</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.03687730481052666</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>-0.008054567915335365</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-0.4170193990784554</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-10.95988814731592</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>2.4545891317169</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-10.93378565904395</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.8440183322366179</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-10.90815143065165</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-6.716126945650756</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-18.17141048380564</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-3.638204239751774</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-17.56471416257806</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-3.652192443917483</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-15.71390542992988</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>6.050426341362551</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-3.290318175763043</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>8.351942430816806</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-3.222455030346327</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>5.281076258485983</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-5.510675914567599</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.004496064702922153</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.1181632469760752</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.02616378141252403</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.1165446283038499</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.009052420431847164</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.1169941091478934</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.07026923851575857</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.1923813495012215</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.0378457465087396</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.1843898985439731</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.03828932051036919</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.167029645492888</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.06773911898392036</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>-0.03673398910330052</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.09398663196275471</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>-0.03642935301145666</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.05873064580183054</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>-0.06080189831493272</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>0.690434185975497</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-2.474453586460157</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>2.954718972195058</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-2.989129110357613</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>1.786357629312485</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-2.710453820441017</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-1.765838466239263</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-5.393076527410439</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.4068212337820896</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-5.583293148722824</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-0.0427728889680035</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-4.696241269008016</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>3.551562299346904</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0.3980436679566211</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>5.61537489452892</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.1087486832667257</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>3.543812415965911</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-0.6486485959271584</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>0.007619940257696489</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.02730917570749946</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.03273132269863147</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.03311250593361993</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.01975079290352493</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.02996802611283494</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.01906104470893643</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.05904408795761996</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0.004291636078479393</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.06151935998189464</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.0004678284523971758</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.05159892737456068</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.04012914519333446</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.004338333966569022</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.06308861948232984</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.001210422830588377</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.03979440316859247</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.00727120124575047</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
